--- a/BoEwatch-calculation-examples.xlsx
+++ b/BoEwatch-calculation-examples.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\choiy\Documents\GitHub\Probability-of-BoE-Rate-Hike-or-Cut-Using-3-Month-SONIA-Futures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4929DE71-DB29-454F-A876-842E154FAFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDEF03C-5BBD-45D0-A2A0-A75ED4E49511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31C5425F-BC13-4302-9BBD-3DD5E823DBEE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{31C5425F-BC13-4302-9BBD-3DD5E823DBEE}"/>
   </bookViews>
   <sheets>
     <sheet name="Model_example_using2anchor" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="85">
   <si>
     <t>Implied Rate</t>
   </si>
@@ -558,6 +558,9 @@
   </si>
   <si>
     <t xml:space="preserve">If we are willing to assume the current SONIA rate to be proxy of the target range (which we shouldn't), then we can obtain the implied probability of rate hike/cut. However, that will be more of an expected target range by the market of where rate might be at the end of the current contract. </t>
+  </si>
+  <si>
+    <t>No cut!</t>
   </si>
 </sst>
 </file>
@@ -1776,8 +1779,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="15148112" y="864534"/>
-              <a:ext cx="4323790" cy="2968439"/>
+              <a:off x="15155732" y="820719"/>
+              <a:ext cx="4321885" cy="2781749"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2103,36 +2106,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BC657-1EA8-486E-9F46-909F319FC391}">
   <dimension ref="A1:U56"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="36.5" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" customWidth="1"/>
-    <col min="5" max="5" width="10.625" customWidth="1"/>
-    <col min="7" max="7" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" customWidth="1"/>
+    <col min="5" max="5" width="10.59765625" customWidth="1"/>
+    <col min="7" max="7" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.8984375" customWidth="1"/>
     <col min="10" max="10" width="10.5" customWidth="1"/>
-    <col min="13" max="13" width="19.125" customWidth="1"/>
+    <col min="13" max="13" width="19.09765625" customWidth="1"/>
     <col min="14" max="14" width="15" customWidth="1"/>
     <col min="15" max="15" width="15.5" customWidth="1"/>
     <col min="16" max="16" width="13.5" customWidth="1"/>
     <col min="17" max="17" width="26" customWidth="1"/>
-    <col min="18" max="18" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="30.75" customWidth="1"/>
-    <col min="21" max="21" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.69921875" customWidth="1"/>
+    <col min="21" max="21" width="9.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C1" s="32">
         <f ca="1">TODAY()</f>
-        <v>45818</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+        <v>45830</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>33</v>
       </c>
@@ -2144,7 +2147,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B3" s="28">
         <v>1</v>
       </c>
@@ -2179,7 +2182,7 @@
       <c r="T3" s="15"/>
       <c r="U3" s="16"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -2215,19 +2218,19 @@
       <c r="T4" s="14"/>
       <c r="U4" s="10"/>
     </row>
-    <row r="5" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
       <c r="C5" s="44">
         <v>95.626999999999995</v>
       </c>
       <c r="D5" s="44">
-        <v>95.85</v>
+        <v>95.855000000000004</v>
       </c>
       <c r="E5" s="20">
-        <v>96.045000000000002</v>
+        <v>96.094999999999999</v>
       </c>
       <c r="F5" s="4">
-        <v>96.23</v>
+        <v>45992</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -2236,10 +2239,10 @@
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
     </row>
-    <row r="7" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C8" s="2" t="s">
         <v>1</v>
       </c>
@@ -2250,7 +2253,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>65</v>
       </c>
@@ -2266,47 +2269,45 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C10" s="4">
         <f>D5</f>
-        <v>95.85</v>
+        <v>95.855000000000004</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" ref="D10:D11" si="0">100-C10</f>
-        <v>4.1500000000000057</v>
+        <v>4.144999999999996</v>
       </c>
       <c r="F10" t="s">
         <v>36</v>
       </c>
       <c r="G10" s="33">
-        <f>ABS(R27 - R34)-1</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>56</v>
       </c>
       <c r="C11" s="4">
         <f>E5</f>
-        <v>96.045000000000002</v>
+        <v>96.094999999999999</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>3.9549999999999983</v>
+        <v>3.9050000000000011</v>
       </c>
       <c r="F11" t="s">
         <v>35</v>
       </c>
       <c r="G11" s="33">
-        <f>ABS(R27 - R33)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>81</v>
       </c>
@@ -2318,7 +2319,7 @@
       <c r="M13" s="85"/>
       <c r="N13" s="73"/>
     </row>
-    <row r="14" spans="1:21" ht="45" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B14" s="10"/>
       <c r="C14" s="11" t="s">
         <v>3</v>
@@ -2357,96 +2358,96 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B15" s="35"/>
       <c r="I15" s="9"/>
       <c r="J15" s="67"/>
       <c r="N15" s="9"/>
     </row>
-    <row r="16" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>40</v>
       </c>
       <c r="C16" s="33">
         <f>G10</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D16" s="6">
         <f>C16/(C16+C18)</f>
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="E16" s="61">
+        <v>0</v>
+      </c>
+      <c r="E16" s="61" t="e">
         <f>(E17-(D18*E18))/D16</f>
-        <v>96.128749999999997</v>
-      </c>
-      <c r="F16" s="4">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F16" s="4" t="e">
         <f>100-E16</f>
-        <v>3.8712500000000034</v>
-      </c>
-      <c r="G16" s="4">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G16" s="4" t="e">
         <f>F16-F18</f>
-        <v>-0.50175000000000125</v>
-      </c>
-      <c r="H16" s="38">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H16" s="38" t="e">
         <f>G16/25*100</f>
-        <v>-2.007000000000005</v>
-      </c>
-      <c r="I16" s="23">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I16" s="23" t="e">
         <f>ABS(TRUNC(H16,0))</f>
-        <v>2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J16" s="67"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="9"/>
     </row>
-    <row r="17" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B17" s="36" t="s">
         <v>39</v>
       </c>
       <c r="E17" s="20">
         <f>D5</f>
-        <v>95.85</v>
+        <v>95.855000000000004</v>
       </c>
       <c r="F17" s="4">
         <f t="shared" ref="F17:F19" si="1">100-E17</f>
-        <v>4.1500000000000057</v>
-      </c>
-      <c r="I17" s="24">
+        <v>4.144999999999996</v>
+      </c>
+      <c r="I17" s="24" t="e">
         <f>MOD(ABS(H16),1)</f>
-        <v>7.0000000000050022E-3</v>
-      </c>
-      <c r="J17" s="68">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J17" s="68" t="e">
         <f>IF(I16=0,1-I17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="69">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K17" s="69" t="e">
         <f>IF(I16=0,I17,IF(I16=1,1-I17,0))</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="69">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L17" s="69" t="e">
         <f>IF(I16=0,I17-I17,IF(I16=1,I17,IF(I16=2,1-I17,0)))</f>
-        <v>0.992999999999995</v>
-      </c>
-      <c r="M17" s="69">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M17" s="69" t="e">
         <f>IF(K17 + L17 = 1, 0, IF(I16 = 0, 0, IF(I16 = 1, I17, IF(I16 = 2, I17, IF(I16 = 3, 1 - I17, 0)))))</f>
-        <v>7.0000000000050022E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N17" s="56">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B18" s="36" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="33">
         <f>G11</f>
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6">
         <f>C18/(C18+C16)</f>
-        <v>0.55555555555555558</v>
+        <v>1</v>
       </c>
       <c r="E18" s="4">
         <f>E19</f>
@@ -2462,7 +2463,7 @@
       <c r="M18" s="58"/>
       <c r="N18" s="9"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>5</v>
       </c>
@@ -2484,7 +2485,7 @@
       <c r="M19" s="57"/>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
@@ -2494,11 +2495,11 @@
       <c r="H20" s="15"/>
       <c r="I20" s="15"/>
     </row>
-    <row r="21" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
     </row>
-    <row r="22" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="P22" s="3" t="s">
         <v>54</v>
       </c>
@@ -2506,13 +2507,13 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="Q23" s="46" t="s">
         <v>19</v>
       </c>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="P24" s="27">
         <v>45717</v>
       </c>
@@ -2520,7 +2521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B25" s="3"/>
       <c r="P25" s="27">
         <v>45717</v>
@@ -2533,7 +2534,7 @@
         <v>45785</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C26" s="2" t="s">
         <v>1</v>
       </c>
@@ -2548,18 +2549,21 @@
         <v>22</v>
       </c>
       <c r="R26" s="31"/>
-    </row>
-    <row r="27" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+      <c r="S26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
         <v>57</v>
       </c>
       <c r="C27" s="4">
         <f>E5</f>
-        <v>96.045000000000002</v>
+        <v>96.094999999999999</v>
       </c>
       <c r="D27" s="4">
         <f>100-C27</f>
-        <v>3.9549999999999983</v>
+        <v>3.9050000000000011</v>
       </c>
       <c r="G27" s="33"/>
       <c r="P27" s="27">
@@ -2573,7 +2577,7 @@
         <v>45876</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="P28" s="27">
         <v>45901</v>
       </c>
@@ -2581,7 +2585,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
         <v>62</v>
       </c>
@@ -2603,7 +2607,7 @@
         <v>45967</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B30" s="10"/>
       <c r="C30" s="11" t="s">
         <v>3</v>
@@ -2648,7 +2652,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B31" s="35"/>
       <c r="I31" s="9"/>
       <c r="J31" s="67"/>
@@ -2659,17 +2663,17 @@
       <c r="Q31" s="54"/>
       <c r="R31" s="54"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B32" s="37" t="s">
         <v>56</v>
       </c>
       <c r="E32" s="20">
         <f>C27</f>
-        <v>96.045000000000002</v>
+        <v>96.094999999999999</v>
       </c>
       <c r="F32" s="63">
         <f t="shared" ref="F32" si="2">100-E32</f>
-        <v>3.9549999999999983</v>
+        <v>3.9050000000000011</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="67"/>
@@ -2683,37 +2687,37 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="36" t="s">
         <v>40</v>
       </c>
       <c r="C33" s="33">
         <f>G10</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D33" s="6">
         <f>C33/(C33+C35)</f>
-        <v>0.44444444444444442</v>
+        <v>0</v>
       </c>
       <c r="E33" s="4">
         <f>E32</f>
-        <v>96.045000000000002</v>
+        <v>96.094999999999999</v>
       </c>
       <c r="F33" s="63">
         <f>100-E33</f>
-        <v>3.9549999999999983</v>
+        <v>3.9050000000000011</v>
       </c>
       <c r="G33" s="4">
         <f>F33-F35</f>
-        <v>-0.3510000000000133</v>
+        <v>-0.23999999999999488</v>
       </c>
       <c r="H33" s="38">
         <f>G33/25*100</f>
-        <v>-1.4040000000000532</v>
+        <v>-0.95999999999997965</v>
       </c>
       <c r="I33" s="23">
         <f>ABS(TRUNC(H33,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -2729,37 +2733,37 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>39</v>
       </c>
       <c r="E34" s="20">
         <f>D5</f>
-        <v>95.85</v>
+        <v>95.855000000000004</v>
       </c>
       <c r="F34" s="4">
         <f>100-E34</f>
-        <v>4.1500000000000057</v>
+        <v>4.144999999999996</v>
       </c>
       <c r="I34" s="24">
         <f>MOD(ABS(H33),1)</f>
-        <v>0.40400000000005321</v>
+        <v>0.95999999999997965</v>
       </c>
       <c r="J34" s="68">
         <f>IF(I33=0,1-I34,0)</f>
-        <v>0</v>
+        <v>4.0000000000020353E-2</v>
       </c>
       <c r="K34" s="55">
         <f>IF(I33=0,I34,IF(I33=1,1-I34,0))</f>
-        <v>0.59599999999994679</v>
+        <v>0.95999999999997965</v>
       </c>
       <c r="L34" s="55">
         <f>IF(I33=0,I34-I34,IF(I33=1,I34,IF(I33=2,1-I34,0)))</f>
-        <v>0.40400000000005321</v>
+        <v>0</v>
       </c>
       <c r="M34" s="55">
         <f>IF(K34 + L34 = 1, 0, IF(I33 = 0, I34, IF(I33 = 1, I34, IF(I33 = 2, I34, IF(I33 = 3, 1 - I34, 0)))))</f>
-        <v>0</v>
+        <v>0.95999999999997965</v>
       </c>
       <c r="N34" s="56">
         <v>0</v>
@@ -2775,25 +2779,25 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="37" t="s">
         <v>38</v>
       </c>
       <c r="C35" s="59">
         <f>G11</f>
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D35" s="57">
         <f>C35/(C35+C33)</f>
-        <v>0.55555555555555558</v>
+        <v>1</v>
       </c>
       <c r="E35" s="62">
         <f>((E34)-(D33*E33))/D35</f>
-        <v>95.693999999999988</v>
+        <v>95.855000000000004</v>
       </c>
       <c r="F35" s="60">
         <f>100-E35</f>
-        <v>4.3060000000000116</v>
+        <v>4.144999999999996</v>
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
@@ -2814,25 +2818,25 @@
         <v>46008</v>
       </c>
     </row>
-    <row r="37" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>12</v>
       </c>
       <c r="I38" s="6"/>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="21" t="s">
         <v>4</v>
       </c>
@@ -2840,7 +2844,7 @@
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
     </row>
-    <row r="41" spans="2:18" ht="18.75" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:18" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>45</v>
       </c>
@@ -2848,12 +2852,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="2:18" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>78</v>
       </c>
@@ -2863,7 +2867,7 @@
       <c r="P43" s="65"/>
       <c r="Q43" s="65"/>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="22" t="s">
         <v>48</v>
       </c>
@@ -2876,16 +2880,16 @@
       <c r="O44" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="P44" s="66">
+      <c r="P44" s="66" t="e">
         <f>K17</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q44" s="66">
         <f>K34</f>
-        <v>0.59599999999994679</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+        <v>0.95999999999997965</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>7</v>
       </c>
@@ -2894,14 +2898,14 @@
       </c>
       <c r="P45" s="66">
         <f>L34</f>
-        <v>0.40400000000005321</v>
-      </c>
-      <c r="Q45" s="66">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="66" t="e">
         <f>L17</f>
-        <v>0.992999999999995</v>
-      </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B46" s="25" t="s">
         <v>13</v>
       </c>
@@ -2918,14 +2922,14 @@
       </c>
       <c r="P46" s="66">
         <f>M34</f>
-        <v>0</v>
-      </c>
-      <c r="Q46" s="66">
+        <v>0.95999999999997965</v>
+      </c>
+      <c r="Q46" s="66" t="e">
         <f>M17</f>
-        <v>7.0000000000050022E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="26" t="s">
         <v>79</v>
       </c>
@@ -2939,7 +2943,7 @@
       <c r="J47" s="26"/>
       <c r="K47" s="26"/>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B48" s="26" t="s">
         <v>14</v>
       </c>
@@ -2953,7 +2957,7 @@
       <c r="J48" s="26"/>
       <c r="K48" s="26"/>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" s="26" t="s">
         <v>15</v>
       </c>
@@ -2967,7 +2971,7 @@
       <c r="J49" s="26"/>
       <c r="K49" s="26"/>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="26" t="s">
         <v>16</v>
       </c>
@@ -2981,7 +2985,7 @@
       <c r="J50" s="26"/>
       <c r="K50" s="26"/>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" s="39" t="s">
         <v>17</v>
       </c>
@@ -2996,7 +3000,7 @@
       <c r="K51" s="39"/>
       <c r="L51" s="39"/>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="39" t="s">
         <v>18</v>
       </c>
@@ -3011,7 +3015,7 @@
       <c r="K52" s="39"/>
       <c r="L52" s="39"/>
     </row>
-    <row r="53" spans="2:12" ht="18.75" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:12" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B53" s="39" t="s">
         <v>47</v>
       </c>
@@ -3026,17 +3030,17 @@
       <c r="K53" s="39"/>
       <c r="L53" s="39"/>
     </row>
-    <row r="54" spans="2:12" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B55" s="45" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B56" s="45" t="s">
         <v>52</v>
       </c>
@@ -3069,19 +3073,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F20D9AC1-C1BE-425E-BFE2-9051668BC55F}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -3094,37 +3098,37 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F166E4D-0D17-48C2-B2CB-7100516C71BC}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.125" customWidth="1"/>
-    <col min="2" max="2" width="16.875" customWidth="1"/>
-    <col min="3" max="3" width="14.25" customWidth="1"/>
-    <col min="4" max="4" width="11.125" customWidth="1"/>
-    <col min="5" max="5" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.09765625" customWidth="1"/>
+    <col min="2" max="2" width="16.8984375" customWidth="1"/>
+    <col min="3" max="3" width="14.19921875" customWidth="1"/>
+    <col min="4" max="4" width="11.09765625" customWidth="1"/>
+    <col min="5" max="5" width="18.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C1" s="32">
         <f ca="1">TODAY()</f>
-        <v>45818</v>
+        <v>45830</v>
       </c>
       <c r="G1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C2" s="32">
         <f ca="1">C1</f>
-        <v>45818</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+        <v>45830</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="28">
         <v>1</v>
       </c>
@@ -3141,7 +3145,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -3158,7 +3162,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
       <c r="C5" s="44">
         <f>Model_example_using2anchor!C5</f>
@@ -3166,22 +3170,22 @@
       </c>
       <c r="D5" s="44">
         <f>Model_example_using2anchor!D5</f>
-        <v>95.85</v>
+        <v>95.855000000000004</v>
       </c>
       <c r="E5" s="20">
         <f>Model_example_using2anchor!E5</f>
-        <v>96.045000000000002</v>
+        <v>96.094999999999999</v>
       </c>
       <c r="G5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C8" s="2" t="s">
         <v>1</v>
       </c>
@@ -3192,7 +3196,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>65</v>
       </c>
@@ -3208,33 +3212,33 @@
         <v>4.2119999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C10" s="4">
         <f>Model_example_using2anchor!D5</f>
-        <v>95.85</v>
+        <v>95.855000000000004</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" ref="D10:D12" si="0">100-C10</f>
-        <v>4.1500000000000057</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>4.144999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>56</v>
       </c>
       <c r="C11" s="4">
         <f>Model_example_using2anchor!E5</f>
-        <v>96.045000000000002</v>
+        <v>96.094999999999999</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>3.9549999999999983</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3.9050000000000011</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
         <v>77</v>
       </c>
@@ -3246,10 +3250,10 @@
         <v>3.7750000000000057</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G15" s="76"/>
     </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" s="79" t="s">
         <v>75</v>
       </c>
@@ -3259,7 +3263,7 @@
       <c r="F16" s="16"/>
       <c r="G16" s="58"/>
     </row>
-    <row r="17" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="67"/>
       <c r="C17" s="76" t="s">
         <v>71</v>
@@ -3275,17 +3279,17 @@
       </c>
       <c r="G17" s="58"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="74" t="s">
         <v>68</v>
       </c>
       <c r="C18" s="58">
         <f>IF((D10 - E9)/0.25 &lt; 0, 1-(ABS(D18)),0)</f>
-        <v>0.75200000000002376</v>
+        <v>0.73199999999998511</v>
       </c>
       <c r="D18" s="83">
         <f>IF((D10 - E9)/0.25 &gt; 0, E18 - 1, (D10 - E9)/0.25)</f>
-        <v>-0.24799999999997624</v>
+        <v>-0.26800000000001489</v>
       </c>
       <c r="E18" s="58">
         <f>IF((D10 - E9)/0.25 &gt; 0, MOD((D10 - E9)/0.25, 1), 0)</f>
@@ -3293,17 +3297,17 @@
       </c>
       <c r="F18" s="78"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="75" t="s">
         <v>56</v>
       </c>
       <c r="C19" s="58">
         <f>IF((D11 - E9)/0.25 &lt; 0, 1-(ABS(D19)),0)</f>
-        <v>-2.8000000000005798E-2</v>
+        <v>-0.22799999999999443</v>
       </c>
       <c r="D19" s="83">
         <f>IF((D11 - E9)/0.25 &gt; 0, E19 - 1, (D11 - E9)/0.25)</f>
-        <v>-1.0280000000000058</v>
+        <v>-1.2279999999999944</v>
       </c>
       <c r="E19" s="58">
         <f>IF((D11 - E9)/0.25 &gt; 0, MOD((D11 - E9)/0.25, 1), 0)</f>
@@ -3311,18 +3315,18 @@
       </c>
       <c r="F19" s="80"/>
     </row>
-    <row r="22" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="81" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="E25">
         <f>IF((D10 - E9)/0.25 &gt; 0, E18 - 1, (D10 - E9)/0.25)</f>
-        <v>-0.24799999999997624</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+        <v>-0.26800000000001489</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="E28" s="82"/>
     </row>
   </sheetData>

--- a/BoEwatch-calculation-examples.xlsx
+++ b/BoEwatch-calculation-examples.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\choiy\Documents\GitHub\Probability-of-BoE-Rate-Hike-or-Cut-Using-3-Month-SONIA-Futures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDEF03C-5BBD-45D0-A2A0-A75ED4E49511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BACB18-E35A-411A-BC88-5870D241A027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{31C5425F-BC13-4302-9BBD-3DD5E823DBEE}"/>
+    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{31C5425F-BC13-4302-9BBD-3DD5E823DBEE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Model_example_using2anchor" sheetId="3" r:id="rId1"/>
+    <sheet name="Model_example" sheetId="3" r:id="rId1"/>
     <sheet name="Note_using the next Q as anchor" sheetId="4" r:id="rId2"/>
     <sheet name="CFA_Methodology_not useful" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Model_example_using2anchor!$O$44</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Model_example_using2anchor!$O$45</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Model_example_using2anchor!$P$44:$Q$44</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Model_example_using2anchor!$P$45:$Q$45</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Model_example!$O$48</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Model_example!$O$49</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Model_example!$P$48:$Q$48</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Model_example!$P$49:$Q$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="78">
   <si>
     <t>Implied Rate</t>
   </si>
@@ -101,45 +101,6 @@
     <t xml:space="preserve">        9.1. As a reminder, each successive FOMC month will add a branch to this probability tree. That means one or more extra probability to calculate.</t>
   </si>
   <si>
-    <t>February: Thursday, February 6</t>
-  </si>
-  <si>
-    <t>March: Thursday, March 20</t>
-  </si>
-  <si>
-    <t>May: Thursday, May 8</t>
-  </si>
-  <si>
-    <t>June: Thursday, June 19</t>
-  </si>
-  <si>
-    <t>August: Thursday, August 7</t>
-  </si>
-  <si>
-    <t>September: Thursday, September 18</t>
-  </si>
-  <si>
-    <t>November: Thursday, November 6</t>
-  </si>
-  <si>
-    <t>December: Thursday, December 18</t>
-  </si>
-  <si>
-    <t>Bank of England's (BoE) Monetary Policy Committee (MPC) meeting schedule for 2025</t>
-  </si>
-  <si>
-    <t>March: March 19, 2025</t>
-  </si>
-  <si>
-    <t>June: June 18, 2025</t>
-  </si>
-  <si>
-    <t>September: September 17, 2025</t>
-  </si>
-  <si>
-    <t>December: December 17, 2025</t>
-  </si>
-  <si>
     <t>Contract start date:</t>
   </si>
   <si>
@@ -153,18 +114,6 @@
   </si>
   <si>
     <t>M -&gt;</t>
-  </si>
-  <si>
-    <t>Q2</t>
-  </si>
-  <si>
-    <t>Q3 (Start)</t>
-  </si>
-  <si>
-    <t>Q3 (Avg)</t>
-  </si>
-  <si>
-    <t>Q3 (End)</t>
   </si>
   <si>
     <t># of 25bp Hikes/Cut</t>
@@ -294,18 +243,12 @@
     <t>We can take this into consideration and caveat, or assuming that SONIA(End)T = SONIA(Avg)T-1, where T is the Quarter the Future Contract covers over which we are interested in the MOC's probability of rate hike/cut.# (i.e. T-1 is the anchor period)</t>
   </si>
   <si>
-    <t>Future Contract</t>
-  </si>
-  <si>
     <t>Quarterly Change</t>
   </si>
   <si>
     <t>Q4</t>
   </si>
   <si>
-    <t>Q4 (Anchor 3-month contract)</t>
-  </si>
-  <si>
     <t>Cut Size</t>
   </si>
   <si>
@@ -318,46 +261,6 @@
     <t>75 bp</t>
   </si>
   <si>
-    <t>Using Q4 as an Anchor month</t>
-  </si>
-  <si>
-    <r>
-      <t>Hike/Cut Size Probabilities</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>for the next 2 MPC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> meeting</t>
-    </r>
-  </si>
-  <si>
     <t>2. Find the nearest upcoming month without an MPC meeting.</t>
   </si>
   <si>
@@ -373,58 +276,6 @@
     <t>Q3</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">M = # of days </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>after</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> the LAST MPC until the delivery date of the 3-months SONIA contract</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">N = # of days </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>before</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> the LAST MPC that the 3-months SONIA contract cover </t>
-    </r>
-  </si>
-  <si>
     <t>0bps</t>
   </si>
   <si>
@@ -453,9 +304,6 @@
   </si>
   <si>
     <t>Sources:</t>
-  </si>
-  <si>
-    <t>Using Q2 as an Anchor month</t>
   </si>
   <si>
     <r>
@@ -560,7 +408,185 @@
     <t xml:space="preserve">If we are willing to assume the current SONIA rate to be proxy of the target range (which we shouldn't), then we can obtain the implied probability of rate hike/cut. However, that will be more of an expected target range by the market of where rate might be at the end of the current contract. </t>
   </si>
   <si>
-    <t>No cut!</t>
+    <t>May</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">M = # of days </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>after</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the LAST MPC until the delivery date of the 1-months SONIA contract</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">N = # of days </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>before</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the LAST MPC that the 1-months SONIA contract cover </t>
+    </r>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>June (Start)</t>
+  </si>
+  <si>
+    <t>June (Avg)</t>
+  </si>
+  <si>
+    <t>June (End)</t>
+  </si>
+  <si>
+    <t>April (End)</t>
+  </si>
+  <si>
+    <t>April (Avg)</t>
+  </si>
+  <si>
+    <t>April (Start)</t>
+  </si>
+  <si>
+    <t>No meeting</t>
+  </si>
+  <si>
+    <t>Meet at 18</t>
+  </si>
+  <si>
+    <t>Meet on 30</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># of 25bp </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hikes</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cut</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Hike/Cut Size Probabilities</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for the next MPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> meeting</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Hike/Cut Size Probabilities</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for the next  MPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> meeting</t>
+    </r>
+  </si>
+  <si>
+    <t>(Context: Iran-US/Israel War)</t>
   </si>
 </sst>
 </file>
@@ -572,7 +598,7 @@
     <numFmt numFmtId="165" formatCode="&quot;Quarter &quot;0"/>
     <numFmt numFmtId="166" formatCode="0%;0%;0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -652,8 +678,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -681,24 +715,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -877,7 +893,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -923,13 +939,8 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -939,26 +950,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
     <xf numFmtId="9" fontId="2" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="2" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -1012,6 +1010,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1070,109 +1081,1110 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
-  <cx:chartData>
-    <cx:data id="0">
-      <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.2</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="1">
-      <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.3</cx:f>
-      </cx:numDim>
-    </cx:data>
-  </cx:chartData>
-  <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0">
-      <cx:tx>
-        <cx:rich>
-          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr algn="ctr" rtl="0">
-              <a:defRPr/>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:rPr lang="en-GB" b="1"/>
+              <a:t>Probability of rate hike - April meeting</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Model_example!$J$19:$K$19</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0bps</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25bps</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Model_example!$J$23:$K$23</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.33999999999997499</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.66000000000002501</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-419E-4D22-B122-FAD6AF543E4F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="745472736"/>
+        <c:axId val="745469376"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Model_example!$J$19:$K$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>0bps</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>25bps</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Model_example!$J$20:$K$20</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="2"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-419E-4D22-B122-FAD6AF543E4F}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Model_example!$J$19:$K$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>0bps</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>25bps</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Model_example!$J$21:$K$21</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="2"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-419E-4D22-B122-FAD6AF543E4F}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent3"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Model_example!$J$19:$K$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>0bps</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>25bps</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Model_example!$J$22:$K$22</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="2"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-419E-4D22-B122-FAD6AF543E4F}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="745472736"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="745469376"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="745469376"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="745472736"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:srgbClr>
                 </a:solidFill>
-                <a:latin typeface="Arial" panose="020B0604020202020204"/>
               </a:rPr>
-              <a:t>Range of rate </a:t>
+              <a:t>Probability of rate hike - June meeting</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="1" i="1" u="none" strike="noStrike" baseline="0">
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Model_example!$J$31:$K$31</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0bps</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25bps</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Model_example!$J$34:$K$34</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.35384615384617746</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.64615384615382254</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-CE41-4870-9617-0CC4DFF58C97}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1137929232"/>
+        <c:axId val="1137929712"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Model_example!$J$31:$K$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>0bps</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>25bps</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Model_example!$J$32:$K$32</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="2"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-CE41-4870-9617-0CC4DFF58C97}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Model_example!$J$31:$K$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>0bps</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>25bps</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Model_example!$J$33:$K$33</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="2"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-CE41-4870-9617-0CC4DFF58C97}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1137929232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-                <a:latin typeface="Arial" panose="020B0604020202020204"/>
-              </a:rPr>
-              <a:t>cut</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000">
+                  <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
-                  </a:srgbClr>
+                  </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Arial" panose="020B0604020202020204"/>
-              </a:rPr>
-              <a:t> probability from Jun - Sep 2025 as of 23 May</a:t>
-            </a:r>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
-        </cx:rich>
-      </cx:tx>
-    </cx:title>
-    <cx:plotArea>
-      <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{F172C1B1-4B23-48BD-99D9-58E38182A4A3}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.0</cx:f>
-              <cx:v>25 bp</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="0"/>
-          <cx:layoutPr>
-            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{4DE4518D-7DB3-4762-A228-5F22CE802E6B}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.1</cx:f>
-              <cx:v>50 bp</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="1"/>
-          <cx:layoutPr>
-            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-      </cx:plotAreaRegion>
-      <cx:axis id="0" hidden="1">
-        <cx:catScaling gapWidth="1"/>
-        <cx:tickLabels/>
-      </cx:axis>
-      <cx:axis id="1">
-        <cx:valScaling/>
-        <cx:majorGridlines/>
-        <cx:tickLabels/>
-      </cx:axis>
-    </cx:plotArea>
-    <cx:legend pos="t" align="ctr" overlay="0"/>
-  </cx:chart>
-</cx:chartSpace>
+        </c:txPr>
+        <c:crossAx val="1137929712"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1137929712"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1137929232"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1215,8 +2227,48 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1227,7 +2279,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -1250,7 +2302,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -1273,7 +2325,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -1281,11 +2333,11 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -1310,53 +2362,36 @@
         </a:solidFill>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -1371,8 +2406,10 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
@@ -1380,12 +2417,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
@@ -1395,13 +2429,13 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="9525" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -1420,16 +2454,18 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataTable>
   <cs:downBar>
     <cs:lnRef idx="0"/>
@@ -1500,6 +2536,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -1531,8 +2573,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1587,7 +2629,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
   <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -1615,30 +2657,22 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat">
-        <a:solidFill>
-          <a:srgbClr val="D9D9D9"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -1654,7 +2688,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400"/>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -1670,7 +2704,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDash"/>
+        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -1684,7 +2718,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
     <cs:lnRef idx="0"/>
@@ -1717,7 +2751,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
@@ -1726,6 +2760,515 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -1735,79 +3278,73 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>784412</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>112059</xdr:rowOff>
+      <xdr:colOff>616324</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>180416</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>145677</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>89648</xdr:rowOff>
+      <xdr:colOff>201707</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>144557</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="3" name="Chart 2">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{786E2D30-98BC-0F37-4682-8276F3EBA5FA}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15155732" y="820719"/>
-              <a:ext cx="4321885" cy="2781749"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-GB" sz="1100"/>
-                <a:t>This chart isn't available in your version of Excel.
-Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C2E0A71-EBFD-2F40-D839-3942A16179B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>818029</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>23531</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>403412</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>166967</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDEA27F2-6C03-A032-7276-CA84FE6D79CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2105,66 +3642,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BC657-1EA8-486E-9F46-909F319FC391}">
-  <dimension ref="A1:U56"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U60"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="36.5" customWidth="1"/>
-    <col min="3" max="3" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" customWidth="1"/>
-    <col min="5" max="5" width="10.59765625" customWidth="1"/>
-    <col min="7" max="7" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.8984375" customWidth="1"/>
+    <col min="3" max="3" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
+    <col min="5" max="5" width="10.625" customWidth="1"/>
+    <col min="7" max="7" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.875" customWidth="1"/>
     <col min="10" max="10" width="10.5" customWidth="1"/>
-    <col min="13" max="13" width="19.09765625" customWidth="1"/>
+    <col min="13" max="13" width="19.125" customWidth="1"/>
     <col min="14" max="14" width="15" customWidth="1"/>
     <col min="15" max="15" width="15.5" customWidth="1"/>
     <col min="16" max="16" width="13.5" customWidth="1"/>
     <col min="17" max="17" width="26" customWidth="1"/>
     <col min="18" max="18" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="30.69921875" customWidth="1"/>
-    <col min="21" max="21" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.75" customWidth="1"/>
+    <col min="21" max="21" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="32">
+        <v>21</v>
+      </c>
+      <c r="C1" s="29">
         <f ca="1">TODAY()</f>
-        <v>45830</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+        <v>46105</v>
+      </c>
+      <c r="D1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="15" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="32">
-        <f>DATEVALUE("10/06/2025")</f>
-        <v>45818</v>
+        <v>20</v>
+      </c>
+      <c r="C2" s="29">
+        <f>DATEVALUE("24/03/2026")</f>
+        <v>46105</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B3" s="28">
-        <v>1</v>
-      </c>
-      <c r="C3" s="40">
-        <v>2</v>
-      </c>
-      <c r="D3" s="41">
-        <v>3</v>
-      </c>
-      <c r="E3" s="28">
-        <v>4</v>
-      </c>
-      <c r="F3" s="28">
-        <v>1</v>
-      </c>
-      <c r="G3" s="28">
-        <v>2</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B3" s="39"/>
+      <c r="C3" s="39">
+        <v>46113</v>
+      </c>
+      <c r="D3" s="39">
+        <v>46143</v>
+      </c>
+      <c r="E3" s="39">
+        <v>46174</v>
+      </c>
+      <c r="F3" s="39">
+        <v>46204</v>
+      </c>
+      <c r="G3" s="39">
+        <v>46235</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -2172,7 +3710,7 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="N3" s="19" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="O3" s="15"/>
       <c r="P3" s="15"/>
@@ -2182,33 +3720,33 @@
       <c r="T3" s="15"/>
       <c r="U3" s="16"/>
     </row>
-    <row r="4" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="29">
-        <v>45627</v>
-      </c>
-      <c r="C4" s="42">
-        <v>45717</v>
-      </c>
-      <c r="D4" s="43">
-        <v>45809</v>
-      </c>
-      <c r="E4" s="29">
-        <v>45901</v>
-      </c>
-      <c r="F4" s="30">
-        <v>45992</v>
-      </c>
-      <c r="G4" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="B4" s="28"/>
+      <c r="C4" s="78" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="79" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="80" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="81" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="82" t="s">
+        <v>71</v>
+      </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="N4" s="17" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O4" s="14"/>
       <c r="P4" s="14"/>
@@ -2218,19 +3756,19 @@
       <c r="T4" s="14"/>
       <c r="U4" s="10"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="15" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
-      <c r="C5" s="44">
-        <v>95.626999999999995</v>
-      </c>
-      <c r="D5" s="44">
-        <v>95.855000000000004</v>
+      <c r="C5" s="41">
+        <v>96.265000000000001</v>
+      </c>
+      <c r="D5" s="41">
+        <v>96.1</v>
       </c>
       <c r="E5" s="20">
-        <v>96.094999999999999</v>
+        <v>96.03</v>
       </c>
       <c r="F5" s="4">
-        <v>45992</v>
+        <v>95.86</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -2239,830 +3777,787 @@
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="15" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B9" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" s="4">
         <f>C5</f>
-        <v>95.626999999999995</v>
+        <v>96.265000000000001</v>
       </c>
       <c r="D9" s="4">
         <f>100-C9</f>
-        <v>4.3730000000000047</v>
-      </c>
-      <c r="F9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+        <v>3.7349999999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C10" s="4">
         <f>D5</f>
-        <v>95.855000000000004</v>
+        <v>96.1</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" ref="D10:D11" si="0">100-C10</f>
-        <v>4.144999999999996</v>
-      </c>
-      <c r="F10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+        <v>3.9000000000000057</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B11" s="7" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C11" s="4">
         <f>E5</f>
-        <v>96.094999999999999</v>
+        <v>96.03</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>3.9050000000000011</v>
-      </c>
-      <c r="F11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="33">
+        <v>3.9699999999999989</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+      <c r="B14" s="3"/>
+      <c r="F14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="C15" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J13" s="84" t="s">
-        <v>63</v>
-      </c>
-      <c r="K13" s="85"/>
-      <c r="L13" s="85"/>
-      <c r="M13" s="85"/>
-      <c r="N13" s="73"/>
-    </row>
-    <row r="14" spans="1:21" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B14" s="10"/>
-      <c r="C14" s="11" t="s">
+      <c r="D15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="4">
+        <f>D5</f>
+        <v>96.1</v>
+      </c>
+      <c r="D16" s="4">
+        <f>100-C16</f>
+        <v>3.9000000000000057</v>
+      </c>
+      <c r="F16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="30">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J18" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="K18" s="73"/>
+      <c r="L18" s="73"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="61"/>
+    </row>
+    <row r="19" spans="1:14" ht="45" x14ac:dyDescent="0.2">
+      <c r="B19" s="10"/>
+      <c r="C19" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D19" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E19" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F19" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="G14" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="H14" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="70" t="s">
-        <v>71</v>
-      </c>
-      <c r="K14" s="71" t="s">
+      <c r="G19" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" s="58" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="71" t="s">
+      <c r="L19" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="M14" s="71" t="s">
+      <c r="M19" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="72" t="s">
+      <c r="N19" s="60" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B15" s="35"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="67"/>
-      <c r="N15" s="9"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B16" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="33">
-        <f>G10</f>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B20" s="32"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="55"/>
+      <c r="N20" s="9"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="20">
+        <f>D5</f>
+        <v>96.1</v>
+      </c>
+      <c r="F21" s="51">
+        <f t="shared" ref="F21" si="1">100-E21</f>
+        <v>3.9000000000000057</v>
+      </c>
+      <c r="I21" s="9"/>
+      <c r="J21" s="55"/>
+      <c r="L21" s="46"/>
+      <c r="M21" s="46"/>
+      <c r="N21" s="9"/>
+    </row>
+    <row r="22" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B22" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="30">
+        <f>G15</f>
         <v>0</v>
       </c>
-      <c r="D16" s="6">
-        <f>C16/(C16+C18)</f>
+      <c r="D22" s="6">
+        <f>C22/(C22+C24)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="61" t="e">
-        <f>(E17-(D18*E18))/D16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F16" s="4" t="e">
-        <f>100-E16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G16" s="4" t="e">
-        <f>F16-F18</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H16" s="38" t="e">
-        <f>G16/25*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I16" s="23" t="e">
-        <f>ABS(TRUNC(H16,0))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J16" s="67"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="9"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B17" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="20">
-        <f>D5</f>
-        <v>95.855000000000004</v>
-      </c>
-      <c r="F17" s="4">
-        <f t="shared" ref="F17:F19" si="1">100-E17</f>
-        <v>4.144999999999996</v>
-      </c>
-      <c r="I17" s="24" t="e">
-        <f>MOD(ABS(H16),1)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J17" s="68" t="e">
-        <f>IF(I16=0,1-I17,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K17" s="69" t="e">
-        <f>IF(I16=0,I17,IF(I16=1,1-I17,0))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L17" s="69" t="e">
-        <f>IF(I16=0,I17-I17,IF(I16=1,I17,IF(I16=2,1-I17,0)))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M17" s="69" t="e">
-        <f>IF(K17 + L17 = 1, 0, IF(I16 = 0, 0, IF(I16 = 1, I17, IF(I16 = 2, I17, IF(I16 = 3, 1 - I17, 0)))))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N17" s="56">
+      <c r="E22" s="4">
+        <f>E21</f>
+        <v>96.1</v>
+      </c>
+      <c r="F22" s="51">
+        <f>100-E22</f>
+        <v>3.9000000000000057</v>
+      </c>
+      <c r="G22" s="4">
+        <f>F22-F24</f>
+        <v>0.16500000000000625</v>
+      </c>
+      <c r="H22" s="35">
+        <f>G22/25*100</f>
+        <v>0.66000000000002501</v>
+      </c>
+      <c r="I22" s="23">
+        <f>ABS(TRUNC(H22,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B18" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="33">
-        <f>G11</f>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="9"/>
+    </row>
+    <row r="23" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B23" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="20">
+        <f>C5</f>
+        <v>96.265000000000001</v>
+      </c>
+      <c r="F23" s="4">
+        <f>100-E23</f>
+        <v>3.7349999999999994</v>
+      </c>
+      <c r="I23" s="24">
+        <f>MOD(ABS(H22),1)</f>
+        <v>0.66000000000002501</v>
+      </c>
+      <c r="J23" s="56">
+        <f>IF(I22=0,1-I23,0)</f>
+        <v>0.33999999999997499</v>
+      </c>
+      <c r="K23" s="43">
+        <f>IF(I22=0,I23,IF(I22=1,1-I23,0))</f>
+        <v>0.66000000000002501</v>
+      </c>
+      <c r="L23" s="43">
+        <f>IF(I22=0,I23-I23,IF(I22=1,I23,IF(I22=2,1-I23,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="43">
+        <v>0</v>
+      </c>
+      <c r="N23" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B24" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="47">
+        <f>G16</f>
+        <v>30</v>
+      </c>
+      <c r="D24" s="45">
+        <f>C24/(C24+C22)</f>
         <v>1</v>
       </c>
-      <c r="D18" s="6">
-        <f>C18/(C18+C16)</f>
+      <c r="E24" s="50">
+        <f>((E23)-(D22*E22))/D24</f>
+        <v>96.265000000000001</v>
+      </c>
+      <c r="F24" s="48">
+        <f>100-E24</f>
+        <v>3.7349999999999994</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="10"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B25" s="74"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="74"/>
+      <c r="K25" s="74"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="74"/>
+    </row>
+    <row r="26" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B26" s="74"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="76"/>
+      <c r="F26" t="s">
+        <v>61</v>
+      </c>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="74"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="74"/>
+    </row>
+    <row r="27" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B27" s="74"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="76"/>
+      <c r="F27" t="s">
+        <v>62</v>
+      </c>
+      <c r="H27" s="74"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="74"/>
+      <c r="K27" s="74"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="74"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B28" s="74"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="76"/>
+      <c r="F28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="30">
+        <v>13</v>
+      </c>
+      <c r="H28" s="74"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="74"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="74"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F29" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="30">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B30" s="3"/>
+      <c r="J30" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="K30" s="73"/>
+      <c r="L30" s="73"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="61"/>
+    </row>
+    <row r="31" spans="1:14" ht="45" x14ac:dyDescent="0.2">
+      <c r="B31" s="10"/>
+      <c r="C31" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E18" s="4">
-        <f>E19</f>
-        <v>95.626999999999995</v>
-      </c>
-      <c r="F18" s="63">
-        <f t="shared" si="1"/>
-        <v>4.3730000000000047</v>
-      </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="67"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="9"/>
-    </row>
-    <row r="19" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="37" t="s">
+      <c r="F31" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="20">
-        <f>C9</f>
-        <v>95.626999999999995</v>
-      </c>
-      <c r="F19" s="63">
-        <f t="shared" si="1"/>
-        <v>4.3730000000000047</v>
-      </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="10"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="P22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="Q23" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="P24" s="27">
-        <v>45717</v>
-      </c>
-      <c r="Q24" s="47" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B25" s="3"/>
-      <c r="P25" s="27">
-        <v>45717</v>
-      </c>
-      <c r="Q25" s="48" t="s">
-        <v>21</v>
-      </c>
-      <c r="R25" s="32">
-        <f>DATEVALUE("08/05/2025")</f>
-        <v>45785</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G26" s="33"/>
-      <c r="P26" s="27">
-        <v>45809</v>
-      </c>
-      <c r="Q26" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="R26" s="31"/>
-      <c r="S26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="4">
-        <f>E5</f>
-        <v>96.094999999999999</v>
-      </c>
-      <c r="D27" s="4">
-        <f>100-C27</f>
-        <v>3.9050000000000011</v>
-      </c>
-      <c r="G27" s="33"/>
-      <c r="P27" s="27">
-        <v>45809</v>
-      </c>
-      <c r="Q27" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="R27" s="32">
-        <f>DATEVALUE("07/08/2025")</f>
-        <v>45876</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="P28" s="27">
-        <v>45901</v>
-      </c>
-      <c r="Q28" s="51" t="s">
+      <c r="H31" s="31" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J29" s="84" t="s">
-        <v>63</v>
-      </c>
-      <c r="K29" s="85"/>
-      <c r="L29" s="85"/>
-      <c r="M29" s="85"/>
-      <c r="N29" s="73"/>
-      <c r="P29" s="27">
-        <v>45901</v>
-      </c>
-      <c r="Q29" s="52" t="s">
+      <c r="I31" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="R29" s="32">
-        <f>DATEVALUE("06/11/2025")</f>
-        <v>45967</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B30" s="10"/>
-      <c r="C30" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="G30" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="H30" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="J30" s="70" t="s">
-        <v>71</v>
-      </c>
-      <c r="K30" s="71" t="s">
+      <c r="J31" s="58" t="s">
+        <v>48</v>
+      </c>
+      <c r="K31" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="L30" s="71" t="s">
+      <c r="L31" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="M30" s="71" t="s">
+      <c r="M31" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="N30" s="72" t="s">
+      <c r="N31" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="P30" s="27">
-        <v>45992</v>
-      </c>
-      <c r="Q30" s="25" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B31" s="35"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="67"/>
-      <c r="N31" s="9"/>
-      <c r="P31" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q31" s="54"/>
-      <c r="R31" s="54"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B32" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="E32" s="20">
-        <f>C27</f>
-        <v>96.094999999999999</v>
-      </c>
-      <c r="F32" s="63">
-        <f t="shared" ref="F32" si="2">100-E32</f>
-        <v>3.9050000000000011</v>
-      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B32" s="32"/>
       <c r="I32" s="9"/>
-      <c r="J32" s="67"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="58"/>
+      <c r="J32" s="55"/>
       <c r="N32" s="9"/>
-      <c r="P32" s="27">
-        <v>45717</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B33" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="33">
-        <f>G10</f>
-        <v>0</v>
+    </row>
+    <row r="33" spans="1:17" ht="15" x14ac:dyDescent="0.25">
+      <c r="B33" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="30">
+        <f>G28</f>
+        <v>13</v>
       </c>
       <c r="D33" s="6">
         <f>C33/(C33+C35)</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="4">
-        <f>E32</f>
-        <v>96.094999999999999</v>
-      </c>
-      <c r="F33" s="63">
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="E33" s="49">
+        <f>(E34-(D35*E35))/D33</f>
+        <v>95.938461538461539</v>
+      </c>
+      <c r="F33" s="4">
         <f>100-E33</f>
-        <v>3.9050000000000011</v>
+        <v>4.0615384615384613</v>
       </c>
       <c r="G33" s="4">
         <f>F33-F35</f>
-        <v>-0.23999999999999488</v>
-      </c>
-      <c r="H33" s="38">
+        <v>0.16153846153845564</v>
+      </c>
+      <c r="H33" s="35">
         <f>G33/25*100</f>
-        <v>-0.95999999999997965</v>
+        <v>0.64615384615382254</v>
       </c>
       <c r="I33" s="23">
         <f>ABS(TRUNC(H33,0))</f>
         <v>0</v>
       </c>
+      <c r="J33" s="55"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="9"/>
-      <c r="P33" s="27">
-        <v>45809</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>29</v>
-      </c>
-      <c r="R33" s="32">
-        <f>DATEVALUE("18/06/2025")</f>
-        <v>45826</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B34" s="36" t="s">
-        <v>39</v>
+    </row>
+    <row r="34" spans="1:17" ht="15" x14ac:dyDescent="0.25">
+      <c r="B34" s="33" t="s">
+        <v>66</v>
       </c>
       <c r="E34" s="20">
-        <f>D5</f>
-        <v>95.855000000000004</v>
+        <f>E5</f>
+        <v>96.03</v>
       </c>
       <c r="F34" s="4">
-        <f>100-E34</f>
-        <v>4.144999999999996</v>
+        <f t="shared" ref="F34:F36" si="2">100-E34</f>
+        <v>3.9699999999999989</v>
       </c>
       <c r="I34" s="24">
         <f>MOD(ABS(H33),1)</f>
-        <v>0.95999999999997965</v>
-      </c>
-      <c r="J34" s="68">
+        <v>0.64615384615382254</v>
+      </c>
+      <c r="J34" s="56">
         <f>IF(I33=0,1-I34,0)</f>
-        <v>4.0000000000020353E-2</v>
-      </c>
-      <c r="K34" s="55">
+        <v>0.35384615384617746</v>
+      </c>
+      <c r="K34" s="57">
         <f>IF(I33=0,I34,IF(I33=1,1-I34,0))</f>
-        <v>0.95999999999997965</v>
-      </c>
-      <c r="L34" s="55">
+        <v>0.64615384615382254</v>
+      </c>
+      <c r="L34" s="57">
         <f>IF(I33=0,I34-I34,IF(I33=1,I34,IF(I33=2,1-I34,0)))</f>
         <v>0</v>
       </c>
-      <c r="M34" s="55">
-        <f>IF(K34 + L34 = 1, 0, IF(I33 = 0, I34, IF(I33 = 1, I34, IF(I33 = 2, I34, IF(I33 = 3, 1 - I34, 0)))))</f>
-        <v>0.95999999999997965</v>
-      </c>
-      <c r="N34" s="56">
+      <c r="M34" s="57">
+        <f>IF(K34 + L34 = 1, 0, IF(I33 = 0, 0, IF(I33 = 1, I34, IF(I33 = 2, I34, IF(I33 = 3, 1 - I34, 0)))))</f>
         <v>0</v>
       </c>
-      <c r="P34" s="27">
-        <v>45901</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>30</v>
-      </c>
-      <c r="R34" s="32">
-        <f>DATEVALUE("17/09/2025")</f>
-        <v>45917</v>
-      </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B35" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="59">
-        <f>G11</f>
-        <v>1</v>
-      </c>
-      <c r="D35" s="57">
+      <c r="N34" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B35" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="30">
+        <f>G29</f>
+        <v>17</v>
+      </c>
+      <c r="D35" s="6">
         <f>C35/(C35+C33)</f>
-        <v>1</v>
-      </c>
-      <c r="E35" s="62">
-        <f>((E34)-(D33*E33))/D35</f>
-        <v>95.855000000000004</v>
-      </c>
-      <c r="F35" s="60">
-        <f>100-E35</f>
-        <v>4.144999999999996</v>
-      </c>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="57"/>
-      <c r="N35" s="10"/>
-      <c r="P35" s="27">
-        <v>45992</v>
-      </c>
-      <c r="Q35" t="s">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="E35" s="4">
+        <f>E36</f>
+        <v>96.1</v>
+      </c>
+      <c r="F35" s="51">
+        <f t="shared" si="2"/>
+        <v>3.9000000000000057</v>
+      </c>
+      <c r="I35" s="9"/>
+      <c r="J35" s="55"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="9"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A36" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="20">
+        <f>C10</f>
+        <v>96.1</v>
+      </c>
+      <c r="F36" s="51">
+        <f t="shared" si="2"/>
+        <v>3.9000000000000057</v>
+      </c>
+      <c r="I36" s="9"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="45"/>
+      <c r="M36" s="45"/>
+      <c r="N36" s="10"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+    </row>
+    <row r="38" spans="1:17" ht="15" x14ac:dyDescent="0.25">
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+    </row>
+    <row r="41" spans="1:17" ht="15" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="I42" s="6"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B43" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B44" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+    </row>
+    <row r="45" spans="1:17" ht="18.75" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
+        <v>28</v>
+      </c>
+      <c r="M45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="15" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>55</v>
+      </c>
+      <c r="O47" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="P47" s="53"/>
+      <c r="Q47" s="53"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B48" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="R35" s="32">
-        <f>DATEVALUE("17/12/2025")</f>
-        <v>46008</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-    </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>12</v>
-      </c>
-      <c r="I38" s="6"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B39" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B40" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-    </row>
-    <row r="41" spans="2:18" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="B41" t="s">
-        <v>45</v>
-      </c>
-      <c r="M41" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B43" t="s">
-        <v>78</v>
-      </c>
-      <c r="O43" s="65" t="s">
-        <v>58</v>
-      </c>
-      <c r="P43" s="65"/>
-      <c r="Q43" s="65"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B44" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="22"/>
-      <c r="O44" s="64" t="s">
-        <v>59</v>
-      </c>
-      <c r="P44" s="66" t="e">
-        <f>K17</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q44" s="66">
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+      <c r="O48" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="P48" s="54">
         <f>K34</f>
-        <v>0.95999999999997965</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
+        <v>0.64615384615382254</v>
+      </c>
+      <c r="Q48" s="54">
+        <f>K23</f>
+        <v>0.66000000000002501</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
         <v>7</v>
       </c>
-      <c r="O45" s="64" t="s">
-        <v>60</v>
-      </c>
-      <c r="P45" s="66">
+      <c r="O49" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="P49" s="54">
+        <f>L23</f>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="54">
         <f>L34</f>
         <v>0</v>
       </c>
-      <c r="Q45" s="66" t="e">
-        <f>L17</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B46" s="25" t="s">
+    </row>
+    <row r="50" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B50" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="25"/>
-      <c r="J46" s="25"/>
-      <c r="O46" s="64" t="s">
-        <v>61</v>
-      </c>
-      <c r="P46" s="66">
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="25"/>
+      <c r="I50" s="25"/>
+      <c r="J50" s="25"/>
+      <c r="O50" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="P50" s="54">
+        <f>M23</f>
+        <v>0</v>
+      </c>
+      <c r="Q50" s="54">
         <f>M34</f>
-        <v>0.95999999999997965</v>
-      </c>
-      <c r="Q46" s="66" t="e">
-        <f>M17</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B47" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="26"/>
-      <c r="K47" s="26"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B48" s="26" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B51" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="26"/>
+      <c r="J51" s="26"/>
+      <c r="K51" s="26"/>
+    </row>
+    <row r="52" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B52" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
-      <c r="H48" s="26"/>
-      <c r="I48" s="26"/>
-      <c r="J48" s="26"/>
-      <c r="K48" s="26"/>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B49" s="26" t="s">
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="26"/>
+      <c r="J52" s="26"/>
+      <c r="K52" s="26"/>
+    </row>
+    <row r="53" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B53" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="26"/>
-      <c r="J49" s="26"/>
-      <c r="K49" s="26"/>
-    </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B50" s="26" t="s">
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="26"/>
+      <c r="J53" s="26"/>
+      <c r="K53" s="26"/>
+    </row>
+    <row r="54" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B54" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="26"/>
-      <c r="G50" s="26"/>
-      <c r="H50" s="26"/>
-      <c r="I50" s="26"/>
-      <c r="J50" s="26"/>
-      <c r="K50" s="26"/>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B51" s="39" t="s">
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="26"/>
+      <c r="J54" s="26"/>
+      <c r="K54" s="26"/>
+    </row>
+    <row r="55" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B55" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="C51" s="39"/>
-      <c r="D51" s="39"/>
-      <c r="E51" s="39"/>
-      <c r="F51" s="39"/>
-      <c r="G51" s="39"/>
-      <c r="H51" s="39"/>
-      <c r="I51" s="39"/>
-      <c r="J51" s="39"/>
-      <c r="K51" s="39"/>
-      <c r="L51" s="39"/>
-    </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B52" s="39" t="s">
+      <c r="C55" s="36"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="36"/>
+      <c r="I55" s="36"/>
+      <c r="J55" s="36"/>
+      <c r="K55" s="36"/>
+      <c r="L55" s="36"/>
+    </row>
+    <row r="56" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B56" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C52" s="39"/>
-      <c r="D52" s="39"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39"/>
-      <c r="G52" s="39"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="39"/>
-      <c r="J52" s="39"/>
-      <c r="K52" s="39"/>
-      <c r="L52" s="39"/>
-    </row>
-    <row r="53" spans="2:12" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="B53" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="C53" s="39"/>
-      <c r="D53" s="39"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="39"/>
-      <c r="G53" s="39"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="39"/>
-      <c r="J53" s="39"/>
-      <c r="K53" s="39"/>
-      <c r="L53" s="39"/>
-    </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B54" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B55" s="45" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B56" s="45" t="s">
-        <v>52</v>
+      <c r="C56" s="36"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="36"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="36"/>
+      <c r="J56" s="36"/>
+      <c r="K56" s="36"/>
+      <c r="L56" s="36"/>
+    </row>
+    <row r="57" spans="2:17" ht="18.75" x14ac:dyDescent="0.35">
+      <c r="B57" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="36"/>
+      <c r="D57" s="36"/>
+      <c r="E57" s="36"/>
+      <c r="F57" s="36"/>
+      <c r="G57" s="36"/>
+      <c r="H57" s="36"/>
+      <c r="I57" s="36"/>
+      <c r="J57" s="36"/>
+      <c r="K57" s="36"/>
+      <c r="L57" s="36"/>
+    </row>
+    <row r="58" spans="2:17" ht="15" x14ac:dyDescent="0.25">
+      <c r="B58" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B59" s="42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B60" s="42" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="J18:M18"/>
   </mergeCells>
-  <conditionalFormatting sqref="H16">
+  <conditionalFormatting sqref="H33">
     <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H33">
+  <conditionalFormatting sqref="H22">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B55" r:id="rId1" display="https://www.cmegroup.com/articles/2023/understanding-the-cme-group-fedwatch-tool-methodology.html" xr:uid="{10B319ED-400D-4054-B0B3-3750263CFCB5}"/>
-    <hyperlink ref="B56" r:id="rId2" display="https://www.ice.com/products/68361266/Three-Month-SONIA-Index-Futures/data" xr:uid="{3602DE27-1F94-4D00-8D21-32FD8B084AD6}"/>
+    <hyperlink ref="B59" r:id="rId1" display="https://www.cmegroup.com/articles/2023/understanding-the-cme-group-fedwatch-tool-methodology.html" xr:uid="{10B319ED-400D-4054-B0B3-3750263CFCB5}"/>
+    <hyperlink ref="B60" r:id="rId2" display="https://www.ice.com/products/68361266/Three-Month-SONIA-Index-Futures/data" xr:uid="{3602DE27-1F94-4D00-8D21-32FD8B084AD6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -3073,21 +4568,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F20D9AC1-C1BE-425E-BFE2-9051668BC55F}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -3098,94 +4593,94 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F166E4D-0D17-48C2-B2CB-7100516C71BC}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.09765625" customWidth="1"/>
-    <col min="2" max="2" width="16.8984375" customWidth="1"/>
-    <col min="3" max="3" width="14.19921875" customWidth="1"/>
-    <col min="4" max="4" width="11.09765625" customWidth="1"/>
-    <col min="5" max="5" width="18.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.125" customWidth="1"/>
+    <col min="2" max="2" width="16.875" customWidth="1"/>
+    <col min="3" max="3" width="14.25" customWidth="1"/>
+    <col min="4" max="4" width="11.125" customWidth="1"/>
+    <col min="5" max="5" width="18.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="32">
+        <v>21</v>
+      </c>
+      <c r="C1" s="29">
         <f ca="1">TODAY()</f>
-        <v>45830</v>
+        <v>46105</v>
       </c>
       <c r="G1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="32">
+        <v>20</v>
+      </c>
+      <c r="C2" s="29">
         <f ca="1">C1</f>
-        <v>45830</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="28">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="B3" s="27">
         <v>1</v>
       </c>
-      <c r="C3" s="40">
+      <c r="C3" s="37">
         <v>2</v>
       </c>
-      <c r="D3" s="41">
+      <c r="D3" s="38">
         <v>3</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="27">
         <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="29">
+        <v>19</v>
+      </c>
+      <c r="B4" s="28">
         <v>45627</v>
       </c>
-      <c r="C4" s="42">
+      <c r="C4" s="39">
         <v>45717</v>
       </c>
-      <c r="D4" s="43">
+      <c r="D4" s="40">
         <v>45809</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="28">
         <v>45901</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
-      <c r="C5" s="44">
-        <f>Model_example_using2anchor!C5</f>
-        <v>95.626999999999995</v>
-      </c>
-      <c r="D5" s="44">
-        <f>Model_example_using2anchor!D5</f>
-        <v>95.855000000000004</v>
+      <c r="C5" s="41">
+        <f>Model_example!C5</f>
+        <v>96.265000000000001</v>
+      </c>
+      <c r="D5" s="41">
+        <f>Model_example!D5</f>
+        <v>96.1</v>
       </c>
       <c r="E5" s="20">
-        <f>Model_example_using2anchor!E5</f>
-        <v>96.094999999999999</v>
+        <f>Model_example!E5</f>
+        <v>96.03</v>
       </c>
       <c r="G5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="C8" s="2" t="s">
         <v>1</v>
       </c>
@@ -3193,54 +4688,54 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9" s="7" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C9" s="4">
-        <f>Model_example_using2anchor!C5</f>
-        <v>95.626999999999995</v>
+        <f>Model_example!C5</f>
+        <v>96.265000000000001</v>
       </c>
       <c r="D9" s="4">
         <f>100-C9</f>
-        <v>4.3730000000000047</v>
+        <v>3.7349999999999994</v>
       </c>
       <c r="E9">
         <v>4.2119999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C10" s="4">
-        <f>Model_example_using2anchor!D5</f>
-        <v>95.855000000000004</v>
+        <f>Model_example!D5</f>
+        <v>96.1</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" ref="D10:D12" si="0">100-C10</f>
-        <v>4.144999999999996</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3.9000000000000057</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11" s="7" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C11" s="4">
-        <f>Model_example_using2anchor!E5</f>
-        <v>96.094999999999999</v>
+        <f>Model_example!E5</f>
+        <v>96.03</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>3.9050000000000011</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3.9699999999999989</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12" s="7" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C12">
         <v>96.224999999999994</v>
@@ -3250,84 +4745,84 @@
         <v>3.7750000000000057</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G15" s="76"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="79" t="s">
-        <v>75</v>
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="G15" s="64"/>
+    </row>
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="B16" s="67" t="s">
+        <v>52</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="16"/>
-      <c r="G16" s="58"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="67"/>
-      <c r="C17" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="76" t="s">
+      <c r="G16" s="46"/>
+    </row>
+    <row r="17" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="B17" s="55"/>
+      <c r="C17" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="76" t="s">
+      <c r="E17" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="77" t="s">
+      <c r="F17" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="G17" s="58"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="74" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" s="58">
+      <c r="G17" s="46"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B18" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="46">
         <f>IF((D10 - E9)/0.25 &lt; 0, 1-(ABS(D18)),0)</f>
-        <v>0.73199999999998511</v>
-      </c>
-      <c r="D18" s="83">
+        <v>-0.24799999999997624</v>
+      </c>
+      <c r="D18" s="71">
         <f>IF((D10 - E9)/0.25 &gt; 0, E18 - 1, (D10 - E9)/0.25)</f>
-        <v>-0.26800000000001489</v>
-      </c>
-      <c r="E18" s="58">
+        <v>-1.2479999999999762</v>
+      </c>
+      <c r="E18" s="46">
         <f>IF((D10 - E9)/0.25 &gt; 0, MOD((D10 - E9)/0.25, 1), 0)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="78"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="58">
+      <c r="F18" s="66"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B19" s="63" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="46">
         <f>IF((D11 - E9)/0.25 &lt; 0, 1-(ABS(D19)),0)</f>
-        <v>-0.22799999999999443</v>
-      </c>
-      <c r="D19" s="83">
+        <v>3.1999999999996476E-2</v>
+      </c>
+      <c r="D19" s="71">
         <f>IF((D11 - E9)/0.25 &gt; 0, E19 - 1, (D11 - E9)/0.25)</f>
-        <v>-1.2279999999999944</v>
-      </c>
-      <c r="E19" s="58">
+        <v>-0.96800000000000352</v>
+      </c>
+      <c r="E19" s="46">
         <f>IF((D11 - E9)/0.25 &gt; 0, MOD((D11 - E9)/0.25, 1), 0)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="80"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="81" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F19" s="68"/>
+    </row>
+    <row r="22" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="B22" s="69" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="E25">
         <f>IF((D10 - E9)/0.25 &gt; 0, E18 - 1, (D10 - E9)/0.25)</f>
-        <v>-0.26800000000001489</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E28" s="82"/>
+        <v>-1.2479999999999762</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="E28" s="70"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D18:D19">

--- a/BoEwatch-calculation-examples.xlsx
+++ b/BoEwatch-calculation-examples.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\choiy\Documents\GitHub\Probability-of-BoE-Rate-Hike-or-Cut-Using-3-Month-SONIA-Futures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\choiy\Documents\GitHub\Probability-of-BoE-Rate-Hike-or-Cut-Using-1-Month-SONIA-Futures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BACB18-E35A-411A-BC88-5870D241A027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E360BAB-B1BC-4212-AFAB-3CE92B9859A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{31C5425F-BC13-4302-9BBD-3DD5E823DBEE}"/>
   </bookViews>
@@ -17,12 +17,6 @@
     <sheet name="Note_using the next Q as anchor" sheetId="4" r:id="rId2"/>
     <sheet name="CFA_Methodology_not useful" sheetId="5" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Model_example!$O$48</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Model_example!$O$49</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Model_example!$P$48:$Q$48</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Model_example!$P$49:$Q$49</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -893,7 +887,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1006,16 +1000,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1023,6 +1007,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1249,10 +1239,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.33999999999997499</c:v>
+                  <c:v>0.48000000000001819</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.66000000000002501</c:v>
+                  <c:v>0.51999999999998181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1349,7 +1339,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Model_example!$J$19:$K$19</c15:sqref>
@@ -1369,7 +1359,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Model_example!$J$21:$K$21</c15:sqref>
@@ -1382,7 +1372,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-419E-4D22-B122-FAD6AF543E4F}"/>
                   </c:ext>
@@ -1405,7 +1395,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Model_example!$J$19:$K$19</c15:sqref>
@@ -1425,7 +1415,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Model_example!$J$22:$K$22</c15:sqref>
@@ -1438,7 +1428,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000002-419E-4D22-B122-FAD6AF543E4F}"/>
                   </c:ext>
@@ -1775,10 +1765,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.35384615384617746</c:v>
+                  <c:v>0.12307692307695106</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.64615384615382254</c:v>
+                  <c:v>0.87692307692304894</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1970,7 +1960,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -1992,7 +1982,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Model_example!$J$31:$K$31</c15:sqref>
@@ -2012,7 +2002,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Model_example!$J$33:$K$33</c15:sqref>
@@ -2025,7 +2015,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-CE41-4870-9617-0CC4DFF58C97}"/>
                   </c:ext>
@@ -3278,15 +3268,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>616324</xdr:colOff>
+      <xdr:colOff>537883</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>180416</xdr:rowOff>
+      <xdr:rowOff>113181</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>201707</xdr:colOff>
+      <xdr:colOff>123266</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>144557</xdr:rowOff>
+      <xdr:rowOff>77322</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3669,7 +3659,7 @@
       </c>
       <c r="C1" s="29">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46110</v>
       </c>
       <c r="D1" t="s">
         <v>77</v>
@@ -3725,19 +3715,19 @@
         <v>19</v>
       </c>
       <c r="B4" s="28"/>
-      <c r="C4" s="78" t="s">
+      <c r="C4" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="79" t="s">
+      <c r="D4" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="80" t="s">
+      <c r="E4" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="81" t="s">
+      <c r="F4" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="82" t="s">
+      <c r="G4" s="76" t="s">
         <v>71</v>
       </c>
       <c r="H4" s="2"/>
@@ -3762,10 +3752,10 @@
         <v>96.265000000000001</v>
       </c>
       <c r="D5" s="41">
-        <v>96.1</v>
+        <v>96.135000000000005</v>
       </c>
       <c r="E5" s="20">
-        <v>96.03</v>
+        <v>96.04</v>
       </c>
       <c r="F5" s="4">
         <v>95.86</v>
@@ -3807,11 +3797,11 @@
       </c>
       <c r="C10" s="4">
         <f>D5</f>
-        <v>96.1</v>
+        <v>96.135000000000005</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" ref="D10:D11" si="0">100-C10</f>
-        <v>3.9000000000000057</v>
+        <v>3.8649999999999949</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
@@ -3820,11 +3810,11 @@
       </c>
       <c r="C11" s="4">
         <f>E5</f>
-        <v>96.03</v>
+        <v>96.04</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>3.9699999999999989</v>
+        <v>3.9599999999999937</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="15" x14ac:dyDescent="0.25">
@@ -3858,11 +3848,11 @@
       </c>
       <c r="C16" s="4">
         <f>D5</f>
-        <v>96.1</v>
+        <v>96.135000000000005</v>
       </c>
       <c r="D16" s="4">
         <f>100-C16</f>
-        <v>3.9000000000000057</v>
+        <v>3.8649999999999949</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
@@ -3875,12 +3865,12 @@
       <c r="B18" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J18" s="72" t="s">
+      <c r="J18" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="K18" s="73"/>
-      <c r="L18" s="73"/>
-      <c r="M18" s="73"/>
+      <c r="K18" s="78"/>
+      <c r="L18" s="78"/>
+      <c r="M18" s="78"/>
       <c r="N18" s="61"/>
     </row>
     <row r="19" spans="1:14" ht="45" x14ac:dyDescent="0.2">
@@ -3937,11 +3927,11 @@
       </c>
       <c r="E21" s="20">
         <f>D5</f>
-        <v>96.1</v>
+        <v>96.135000000000005</v>
       </c>
       <c r="F21" s="51">
         <f t="shared" ref="F21" si="1">100-E21</f>
-        <v>3.9000000000000057</v>
+        <v>3.8649999999999949</v>
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="55"/>
@@ -3963,19 +3953,19 @@
       </c>
       <c r="E22" s="4">
         <f>E21</f>
-        <v>96.1</v>
+        <v>96.135000000000005</v>
       </c>
       <c r="F22" s="51">
         <f>100-E22</f>
-        <v>3.9000000000000057</v>
+        <v>3.8649999999999949</v>
       </c>
       <c r="G22" s="4">
         <f>F22-F24</f>
-        <v>0.16500000000000625</v>
+        <v>0.12999999999999545</v>
       </c>
       <c r="H22" s="35">
         <f>G22/25*100</f>
-        <v>0.66000000000002501</v>
+        <v>0.51999999999998181</v>
       </c>
       <c r="I22" s="23">
         <f>ABS(TRUNC(H22,0))</f>
@@ -3999,15 +3989,15 @@
       </c>
       <c r="I23" s="24">
         <f>MOD(ABS(H22),1)</f>
-        <v>0.66000000000002501</v>
+        <v>0.51999999999998181</v>
       </c>
       <c r="J23" s="56">
         <f>IF(I22=0,1-I23,0)</f>
-        <v>0.33999999999997499</v>
+        <v>0.48000000000001819</v>
       </c>
       <c r="K23" s="43">
         <f>IF(I22=0,I23,IF(I22=1,1-I23,0))</f>
-        <v>0.66000000000002501</v>
+        <v>0.51999999999998181</v>
       </c>
       <c r="L23" s="43">
         <f>IF(I22=0,I23-I23,IF(I22=1,I23,IF(I22=2,1-I23,0)))</f>
@@ -4050,70 +4040,45 @@
       <c r="N24" s="10"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B25" s="74"/>
-      <c r="C25" s="75"/>
+      <c r="C25" s="30"/>
       <c r="D25" s="46"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
-      <c r="I25" s="74"/>
-      <c r="J25" s="74"/>
-      <c r="K25" s="74"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="4"/>
       <c r="L25" s="46"/>
       <c r="M25" s="46"/>
-      <c r="N25" s="74"/>
     </row>
     <row r="26" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B26" s="74"/>
-      <c r="C26" s="75"/>
+      <c r="C26" s="30"/>
       <c r="D26" s="46"/>
-      <c r="E26" s="76"/>
+      <c r="E26" s="49"/>
       <c r="F26" t="s">
         <v>61</v>
       </c>
-      <c r="H26" s="74"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="74"/>
-      <c r="K26" s="74"/>
       <c r="L26" s="46"/>
       <c r="M26" s="46"/>
-      <c r="N26" s="74"/>
     </row>
     <row r="27" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B27" s="74"/>
-      <c r="C27" s="75"/>
+      <c r="C27" s="30"/>
       <c r="D27" s="46"/>
-      <c r="E27" s="76"/>
+      <c r="E27" s="49"/>
       <c r="F27" t="s">
         <v>62</v>
       </c>
-      <c r="H27" s="74"/>
-      <c r="I27" s="74"/>
-      <c r="J27" s="74"/>
-      <c r="K27" s="74"/>
       <c r="L27" s="46"/>
       <c r="M27" s="46"/>
-      <c r="N27" s="74"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B28" s="74"/>
-      <c r="C28" s="75"/>
+      <c r="C28" s="30"/>
       <c r="D28" s="46"/>
-      <c r="E28" s="76"/>
+      <c r="E28" s="49"/>
       <c r="F28" t="s">
         <v>23</v>
       </c>
       <c r="G28" s="30">
         <v>13</v>
       </c>
-      <c r="H28" s="74"/>
-      <c r="I28" s="74"/>
-      <c r="J28" s="74"/>
-      <c r="K28" s="74"/>
       <c r="L28" s="46"/>
       <c r="M28" s="46"/>
-      <c r="N28" s="74"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="F29" t="s">
@@ -4125,12 +4090,12 @@
     </row>
     <row r="30" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B30" s="3"/>
-      <c r="J30" s="72" t="s">
+      <c r="J30" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="K30" s="73"/>
-      <c r="L30" s="73"/>
-      <c r="M30" s="73"/>
+      <c r="K30" s="78"/>
+      <c r="L30" s="78"/>
+      <c r="M30" s="78"/>
       <c r="N30" s="61"/>
     </row>
     <row r="31" spans="1:14" ht="45" x14ac:dyDescent="0.2">
@@ -4192,19 +4157,19 @@
       </c>
       <c r="E33" s="49">
         <f>(E34-(D35*E35))/D33</f>
-        <v>95.938461538461539</v>
+        <v>95.915769230769243</v>
       </c>
       <c r="F33" s="4">
         <f>100-E33</f>
-        <v>4.0615384615384613</v>
+        <v>4.0842307692307571</v>
       </c>
       <c r="G33" s="4">
         <f>F33-F35</f>
-        <v>0.16153846153845564</v>
+        <v>0.21923076923076223</v>
       </c>
       <c r="H33" s="35">
         <f>G33/25*100</f>
-        <v>0.64615384615382254</v>
+        <v>0.87692307692304894</v>
       </c>
       <c r="I33" s="23">
         <f>ABS(TRUNC(H33,0))</f>
@@ -4221,23 +4186,23 @@
       </c>
       <c r="E34" s="20">
         <f>E5</f>
-        <v>96.03</v>
+        <v>96.04</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" ref="F34:F36" si="2">100-E34</f>
-        <v>3.9699999999999989</v>
+        <v>3.9599999999999937</v>
       </c>
       <c r="I34" s="24">
         <f>MOD(ABS(H33),1)</f>
-        <v>0.64615384615382254</v>
+        <v>0.87692307692304894</v>
       </c>
       <c r="J34" s="56">
         <f>IF(I33=0,1-I34,0)</f>
-        <v>0.35384615384617746</v>
+        <v>0.12307692307695106</v>
       </c>
       <c r="K34" s="57">
         <f>IF(I33=0,I34,IF(I33=1,1-I34,0))</f>
-        <v>0.64615384615382254</v>
+        <v>0.87692307692304894</v>
       </c>
       <c r="L34" s="57">
         <f>IF(I33=0,I34-I34,IF(I33=1,I34,IF(I33=2,1-I34,0)))</f>
@@ -4265,11 +4230,11 @@
       </c>
       <c r="E35" s="4">
         <f>E36</f>
-        <v>96.1</v>
+        <v>96.135000000000005</v>
       </c>
       <c r="F35" s="51">
         <f t="shared" si="2"/>
-        <v>3.9000000000000057</v>
+        <v>3.8649999999999949</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="55"/>
@@ -4286,11 +4251,11 @@
       </c>
       <c r="E36" s="20">
         <f>C10</f>
-        <v>96.1</v>
+        <v>96.135000000000005</v>
       </c>
       <c r="F36" s="51">
         <f t="shared" si="2"/>
-        <v>3.9000000000000057</v>
+        <v>3.8649999999999949</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="17"/>
@@ -4377,11 +4342,11 @@
       </c>
       <c r="P48" s="54">
         <f>K34</f>
-        <v>0.64615384615382254</v>
+        <v>0.87692307692304894</v>
       </c>
       <c r="Q48" s="54">
         <f>K23</f>
-        <v>0.66000000000002501</v>
+        <v>0.51999999999998181</v>
       </c>
     </row>
     <row r="49" spans="2:17" x14ac:dyDescent="0.2">
@@ -4545,13 +4510,13 @@
     <mergeCell ref="J30:M30"/>
     <mergeCell ref="J18:M18"/>
   </mergeCells>
-  <conditionalFormatting sqref="H33">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="H22">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H33">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4608,7 +4573,7 @@
       </c>
       <c r="C1" s="29">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46110</v>
       </c>
       <c r="G1" t="s">
         <v>49</v>
@@ -4620,7 +4585,7 @@
       </c>
       <c r="C2" s="29">
         <f ca="1">C1</f>
-        <v>46105</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
@@ -4665,11 +4630,11 @@
       </c>
       <c r="D5" s="41">
         <f>Model_example!D5</f>
-        <v>96.1</v>
+        <v>96.135000000000005</v>
       </c>
       <c r="E5" s="20">
         <f>Model_example!E5</f>
-        <v>96.03</v>
+        <v>96.04</v>
       </c>
       <c r="G5" t="s">
         <v>53</v>
@@ -4713,11 +4678,11 @@
       </c>
       <c r="C10" s="4">
         <f>Model_example!D5</f>
-        <v>96.1</v>
+        <v>96.135000000000005</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" ref="D10:D12" si="0">100-C10</f>
-        <v>3.9000000000000057</v>
+        <v>3.8649999999999949</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -4726,11 +4691,11 @@
       </c>
       <c r="C11" s="4">
         <f>Model_example!E5</f>
-        <v>96.03</v>
+        <v>96.04</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>3.9699999999999989</v>
+        <v>3.9599999999999937</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -4780,11 +4745,11 @@
       </c>
       <c r="C18" s="46">
         <f>IF((D10 - E9)/0.25 &lt; 0, 1-(ABS(D18)),0)</f>
-        <v>-0.24799999999997624</v>
+        <v>-0.38800000000001944</v>
       </c>
       <c r="D18" s="71">
         <f>IF((D10 - E9)/0.25 &gt; 0, E18 - 1, (D10 - E9)/0.25)</f>
-        <v>-1.2479999999999762</v>
+        <v>-1.3880000000000194</v>
       </c>
       <c r="E18" s="46">
         <f>IF((D10 - E9)/0.25 &gt; 0, MOD((D10 - E9)/0.25, 1), 0)</f>
@@ -4798,11 +4763,11 @@
       </c>
       <c r="C19" s="46">
         <f>IF((D11 - E9)/0.25 &lt; 0, 1-(ABS(D19)),0)</f>
-        <v>3.1999999999996476E-2</v>
+        <v>-8.0000000000239879E-3</v>
       </c>
       <c r="D19" s="71">
         <f>IF((D11 - E9)/0.25 &gt; 0, E19 - 1, (D11 - E9)/0.25)</f>
-        <v>-0.96800000000000352</v>
+        <v>-1.008000000000024</v>
       </c>
       <c r="E19" s="46">
         <f>IF((D11 - E9)/0.25 &gt; 0, MOD((D11 - E9)/0.25, 1), 0)</f>
@@ -4818,7 +4783,7 @@
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="E25">
         <f>IF((D10 - E9)/0.25 &gt; 0, E18 - 1, (D10 - E9)/0.25)</f>
-        <v>-1.2479999999999762</v>
+        <v>-1.3880000000000194</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
